--- a/tests/fixtures/lom/28106-1-LOM.xlsx
+++ b/tests/fixtures/lom/28106-1-LOM.xlsx
@@ -76,12 +76,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>28106-1</t>
+          <t>16697-2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>PLATE A</t>
+          <t>LOWER BOOM TUBE 91 1/8 LG.</t>
         </is>
       </c>
     </row>
@@ -113,12 +113,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28106-2</t>
+          <t>26732-1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>PLATE B</t>
+          <t>CYLINDER MOUNT PLATE W/ 3/8 HOLES</t>
         </is>
       </c>
     </row>
@@ -150,12 +150,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>28106-3</t>
+          <t>26732-2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>PLATE C</t>
+          <t>CYLINDER MOUNT PLATE</t>
         </is>
       </c>
     </row>
@@ -187,12 +187,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>28106-4</t>
+          <t>15644-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>PLATE D</t>
+          <t>STIFFENER, CYLINDER MOUNT</t>
         </is>
       </c>
     </row>
@@ -224,12 +224,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>28106-5</t>
+          <t>16694-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>PLATE E</t>
+          <t>STIFFENER, CUTOUT</t>
         </is>
       </c>
     </row>
@@ -261,12 +261,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>28106-6</t>
+          <t>15890-1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>PLATE F</t>
+          <t>END CAP, BOOM</t>
         </is>
       </c>
     </row>
@@ -288,7 +288,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -298,12 +298,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>28106-7</t>
+          <t>15891-1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>PLATE G</t>
+          <t>HOSE GUARD</t>
         </is>
       </c>
     </row>
@@ -335,12 +335,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>28106-8</t>
+          <t>10187-1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>PLATE H</t>
+          <t>HOSE RETAINER</t>
         </is>
       </c>
     </row>
@@ -362,7 +362,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -372,12 +372,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>28106-9</t>
+          <t>15864-2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>PLATE J</t>
+          <t>STIFFENER, BOOM PIVOT</t>
         </is>
       </c>
     </row>
@@ -399,7 +399,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -409,12 +409,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>28106-10</t>
+          <t>15863-1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>PLATE K</t>
+          <t>PIVOT TUBE, LOWER BOOM</t>
         </is>
       </c>
     </row>
@@ -431,12 +431,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -446,12 +446,123 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>28106-11</t>
+          <t>16697-1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>PLATE L</t>
+          <t>LOWER BOOM TUBE 55 LG.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>15654-1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>STIFFENER PLATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>16697-3</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>LOWER BOOM TUBE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>16697-4</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>LOWER BOOM TUBE</t>
         </is>
       </c>
     </row>
@@ -497,12 +608,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>28106-1</t>
+          <t>16697-2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PLATE A</t>
+          <t>LOWER BOOM TUBE 91 1/8 LG.</t>
         </is>
       </c>
     </row>
@@ -519,12 +630,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28106-2</t>
+          <t>26732-1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PLATE B</t>
+          <t>CYLINDER MOUNT PLATE W/ 3/8 HOLES</t>
         </is>
       </c>
     </row>
@@ -541,12 +652,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>28106-3</t>
+          <t>26732-2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PLATE C</t>
+          <t>CYLINDER MOUNT PLATE</t>
         </is>
       </c>
     </row>
@@ -563,12 +674,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>28106-4</t>
+          <t>15644-1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PLATE D</t>
+          <t>STIFFENER, CYLINDER MOUNT</t>
         </is>
       </c>
     </row>
@@ -585,12 +696,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>28106-5</t>
+          <t>16694-1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PLATE E</t>
+          <t>STIFFENER, CUTOUT</t>
         </is>
       </c>
     </row>
@@ -607,19 +718,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>28106-6</t>
+          <t>15890-1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PLATE F</t>
+          <t>END CAP, BOOM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -629,12 +740,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>28106-7</t>
+          <t>15891-1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PLATE G</t>
+          <t>HOSE GUARD</t>
         </is>
       </c>
     </row>
@@ -651,19 +762,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>28106-8</t>
+          <t>10187-1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PLATE H</t>
+          <t>HOSE RETAINER</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -673,19 +784,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>28106-9</t>
+          <t>15864-2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PLATE J</t>
+          <t>STIFFENER, BOOM PIVOT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -695,34 +806,34 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>28106-10</t>
+          <t>15863-1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PLATE K</t>
+          <t>PIVOT TUBE, LOWER BOOM</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>28106-11</t>
+          <t>15654-1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PLATE L</t>
+          <t>STIFFENER PLATE</t>
         </is>
       </c>
     </row>
